--- a/resources/tool_kii_markets_iphra_v2.xlsx
+++ b/resources/tool_kii_markets_iphra_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6420ABD4-D95C-415F-9EDA-77BF4FCB9278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3BE060-235A-45A9-B3FB-171C2FA04BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="240">
   <si>
     <t>type</t>
   </si>
@@ -719,7 +719,49 @@
     <t>market</t>
   </si>
   <si>
-    <t>39001, 39002</t>
+    <t>13001, 13002</t>
+  </si>
+  <si>
+    <t>label::French (fr)</t>
+  </si>
+  <si>
+    <t>Homme</t>
+  </si>
+  <si>
+    <t>Femme</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>Team 1</t>
+  </si>
+  <si>
+    <t>Équipe 1</t>
+  </si>
+  <si>
+    <t>Team 2</t>
+  </si>
+  <si>
+    <t>Équipe 2</t>
+  </si>
+  <si>
+    <t>Team 3</t>
+  </si>
+  <si>
+    <t>Équipe 3</t>
+  </si>
+  <si>
+    <t>Team 4</t>
+  </si>
+  <si>
+    <t>Équipe 4</t>
+  </si>
+  <si>
+    <t>Team 5</t>
+  </si>
+  <si>
+    <t>Équipe 5</t>
   </si>
 </sst>
 </file>
@@ -772,7 +814,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -797,6 +839,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -810,7 +858,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -831,11 +879,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1533,8 +1592,8 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>40002</v>
+      <c r="A18" s="12">
+        <v>13102</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>98</v>
@@ -1547,8 +1606,8 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>40002</v>
+      <c r="A19" s="12">
+        <v>13102</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>
@@ -1561,8 +1620,8 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>40003</v>
+      <c r="A20" s="12">
+        <v>13103</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>129</v>
@@ -1575,8 +1634,8 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>40003</v>
+      <c r="A21" s="12">
+        <v>13103</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>19</v>
@@ -1589,8 +1648,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>41001</v>
+      <c r="A22" s="12">
+        <v>13201</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>129</v>
@@ -1603,8 +1662,8 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>41001</v>
+      <c r="A23" s="12">
+        <v>13201</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>19</v>
@@ -1617,8 +1676,8 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>41002</v>
+      <c r="A24" s="12">
+        <v>13202</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>139</v>
@@ -1631,8 +1690,8 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>41002</v>
+      <c r="A25" s="12">
+        <v>13202</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>19</v>
@@ -1645,7 +1704,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -1656,7 +1715,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -1670,7 +1729,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1684,7 +1743,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -1698,7 +1757,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -1712,7 +1771,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -1726,7 +1785,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -1740,7 +1799,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -1748,8 +1807,8 @@
       </c>
     </row>
     <row r="34" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>40102</v>
+      <c r="A34" s="12">
+        <v>13105</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>17</v>
@@ -1759,8 +1818,8 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>40102</v>
+      <c r="A35" s="12">
+        <v>13105</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>58</v>
@@ -1773,8 +1832,8 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>40102</v>
+      <c r="A36" s="12">
+        <v>13105</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>197</v>
@@ -1787,8 +1846,8 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>40102</v>
+      <c r="A37" s="12">
+        <v>13105</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>197</v>
@@ -1801,8 +1860,8 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>40102</v>
+      <c r="A38" s="12">
+        <v>13105</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>197</v>
@@ -1815,8 +1874,8 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>40102</v>
+      <c r="A39" s="12">
+        <v>13105</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>197</v>
@@ -1829,8 +1888,8 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>40102</v>
+      <c r="A40" s="12">
+        <v>13105</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>197</v>
@@ -1843,16 +1902,16 @@
       </c>
     </row>
     <row r="41" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>40102</v>
+      <c r="A41" s="12">
+        <v>13105</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>40102</v>
+      <c r="A42" s="12">
+        <v>13105</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>19</v>
@@ -1865,7 +1924,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -1879,7 +1938,7 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -1896,7 +1955,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -1910,7 +1969,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -1924,7 +1983,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -1938,7 +1997,7 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -1952,7 +2011,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -1966,7 +2025,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -1974,8 +2033,8 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>41003</v>
+      <c r="A51" s="12">
+        <v>13203</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>129</v>
@@ -1988,8 +2047,8 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>41003</v>
+      <c r="A52" s="12">
+        <v>13203</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>19</v>
@@ -2002,8 +2061,8 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>41003</v>
+      <c r="A53" s="12">
+        <v>13203</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>19</v>
@@ -2058,7 +2117,7 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="C8:C9">
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2066,7 +2125,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D63B81B-C0DE-4D5C-B8D8-1821B93262B2}">
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" style="2" customWidth="1"/>
@@ -2089,6 +2148,9 @@
       <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="6" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
@@ -2301,6 +2363,9 @@
       <c r="D14" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="E14" s="2" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -2315,22 +2380,25 @@
       <c r="D15" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="E15" s="2" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="16" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>10000</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>76</v>
+        <v>229</v>
+      </c>
+      <c r="C16" s="8">
+        <v>1</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>78</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -2338,16 +2406,16 @@
         <v>10000</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>79</v>
+        <v>229</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>78</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -2355,16 +2423,16 @@
         <v>10000</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>80</v>
+        <v>229</v>
+      </c>
+      <c r="C18" s="8">
+        <v>3</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>78</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -2372,16 +2440,16 @@
         <v>10000</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>82</v>
+        <v>229</v>
+      </c>
+      <c r="C19" s="8">
+        <v>4</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>78</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -2389,16 +2457,16 @@
         <v>10000</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>83</v>
+        <v>229</v>
+      </c>
+      <c r="C20" s="8">
+        <v>5</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>78</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -2406,10 +2474,10 @@
         <v>10000</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>77</v>
@@ -2423,10 +2491,10 @@
         <v>10000</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>77</v>
@@ -2440,10 +2508,10 @@
         <v>10000</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>77</v>
@@ -2457,10 +2525,10 @@
         <v>10000</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>77</v>
@@ -2474,10 +2542,10 @@
         <v>10000</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>77</v>
@@ -2491,10 +2559,10 @@
         <v>10000</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>77</v>
@@ -2508,10 +2576,10 @@
         <v>10000</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>77</v>
@@ -2520,494 +2588,657 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>40002</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>113</v>
+    <row r="28" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>40002</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>40002</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>115</v>
+        <v>77</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>40002</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>116</v>
+        <v>77</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>40002</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>117</v>
+        <v>77</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>104</v>
+        <v>77</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>40002</v>
+      <c r="A33" s="12">
+        <v>13102</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>40002</v>
+      <c r="A34" s="12">
+        <v>13102</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>40002</v>
+      <c r="A35" s="12">
+        <v>13102</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>40002</v>
+      <c r="A36" s="12">
+        <v>13102</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>40002</v>
+      <c r="A37" s="12">
+        <v>13102</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>40002</v>
+      <c r="A38" s="12">
+        <v>13102</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>40002</v>
+      <c r="A39" s="12">
+        <v>13102</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>66</v>
+        <v>106</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>40002</v>
+      <c r="A40" s="12">
+        <v>13102</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>40002</v>
+      <c r="A41" s="12">
+        <v>13102</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <v>13102</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <v>13102</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <v>13102</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <v>13102</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <v>13102</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D46" s="8" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="12">
+        <v>13202</v>
+      </c>
       <c r="B47" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <v>13202</v>
+      </c>
       <c r="B48" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <v>13202</v>
+      </c>
       <c r="B49" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <v>13202</v>
+      </c>
       <c r="B50" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="12">
+        <v>13202</v>
+      </c>
       <c r="B51" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <v>13202</v>
+      </c>
       <c r="B52" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <v>13202</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <v>13202</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <v>13202</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <v>13202</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <v>13202</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D57" s="8" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B56" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B57" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>225</v>
+      </c>
       <c r="B58" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D63" s="8" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B59" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B61" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B63" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="12">
+        <v>13105</v>
+      </c>
       <c r="B64" s="2" t="s">
         <v>198</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="12">
+        <v>13105</v>
+      </c>
       <c r="B65" s="2" t="s">
         <v>198</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="12">
+        <v>13105</v>
+      </c>
       <c r="B66" s="2" t="s">
         <v>198</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="12">
+        <v>13105</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="12">
+        <v>13105</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="12">
+        <v>13105</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="12">
+        <v>13105</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="12">
+        <v>13105</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D71" s="8" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D67" s="8"/>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D72" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C6">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C10">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C10">
+  <conditionalFormatting sqref="C11:C12">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
+  <conditionalFormatting sqref="C21:C32">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:C27">
+  <conditionalFormatting sqref="C16:C20">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3050,12 +3281,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3300,20 +3533,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38DBD55A-6A6F-4CFC-88B1-45940F719B9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E67F88-34D7-4F06-AD9D-1E85A09096B5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
+    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3338,12 +3572,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E67F88-34D7-4F06-AD9D-1E85A09096B5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38DBD55A-6A6F-4CFC-88B1-45940F719B9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
-    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>